--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365-my.sharepoint.com/personal/10839715_polimi_it/Documents/Desktop/PhD/SoSym/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365-my.sharepoint.com/personal/10839715_polimi_it/Documents/Desktop/LIRAs_Generation/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="24" documentId="11_0E754C0D39CEB2F96604FAF2FB5AD87B83B7D2CF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{648EEB6D-C3F8-FF4A-A248-F29C7B295FB5}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio 1" sheetId="1" r:id="rId1"/>
@@ -1643,12 +1643,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2831,14 +2831,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="173" customHeight="1">
-      <c r="A1" s="24"/>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
       <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="23.25" customHeight="1">
@@ -2953,7 +2953,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="409.6" customHeight="1">
+    <row r="7" spans="1:7" ht="409.5" customHeight="1">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:7" ht="409.6" customHeight="1">
+    <row r="13" spans="1:7" ht="409.5" customHeight="1">
       <c r="A13" s="10">
         <v>11</v>
       </c>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="G26" s="18"/>
     </row>
-    <row r="27" spans="1:7" ht="409.6" customHeight="1">
+    <row r="27" spans="1:7" ht="409.5" customHeight="1">
       <c r="A27" s="10" cm="1">
         <f t="array" ref="A27">$A26+1</f>
         <v>25</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G29" s="18"/>
     </row>
-    <row r="30" spans="1:7" ht="409.6" customHeight="1">
+    <row r="30" spans="1:7" ht="409.5" customHeight="1">
       <c r="A30" s="10" cm="1">
         <f t="array" ref="A30">$A29+1</f>
         <v>28</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="G36" s="19"/>
     </row>
-    <row r="37" spans="1:7" ht="409.6" customHeight="1">
+    <row r="37" spans="1:7" ht="409.5" customHeight="1">
       <c r="A37" s="10" cm="1">
         <f t="array" ref="A37">$A36+1</f>
         <v>35</v>
